--- a/server/master-excel-files/Kailash_CHEMISTRY_Grade 8.xlsx
+++ b/server/master-excel-files/Kailash_CHEMISTRY_Grade 8.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\teacher-year-plan-app\server\master-excel-files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Teachers year plan\ISAP_CHEMISTRY\NCERT_IIT\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="25">
   <si>
     <t>MONTH</t>
   </si>
@@ -27,12 +27,6 @@
     <t>NCERT SYLLABUS</t>
   </si>
   <si>
-    <t>ASSESSMENTS</t>
-  </si>
-  <si>
-    <t>STATUS</t>
-  </si>
-  <si>
     <t>JUNE</t>
   </si>
   <si>
@@ -42,58 +36,64 @@
     <t>JULY</t>
   </si>
   <si>
-    <t>Periodic Test - 1</t>
-  </si>
-  <si>
     <t>AUGUST</t>
   </si>
   <si>
     <t>SEPTEMBER</t>
   </si>
   <si>
-    <t>Periodic Test - 2</t>
-  </si>
-  <si>
     <t>OCTOBER</t>
   </si>
   <si>
-    <t>Summative Assessment - 1</t>
-  </si>
-  <si>
-    <t>SECTION-1</t>
-  </si>
-  <si>
-    <t>SECTION-2</t>
-  </si>
-  <si>
-    <t>SECTION-3</t>
-  </si>
-  <si>
-    <t>SECTION-4</t>
-  </si>
-  <si>
-    <t>SECTION-5</t>
-  </si>
-  <si>
-    <t>SECTION-6</t>
+    <t>IIT SYLLABUS</t>
+  </si>
+  <si>
+    <t>IIT STATUS</t>
+  </si>
+  <si>
+    <t>NCERT_SEC-1</t>
+  </si>
+  <si>
+    <t>NCERT_SEC-2</t>
+  </si>
+  <si>
+    <t>NCERT_SEC-3</t>
+  </si>
+  <si>
+    <t>NCERT_SEC-4</t>
+  </si>
+  <si>
+    <t>NCERT_SEC-5</t>
+  </si>
+  <si>
+    <t>NCERT_SEC-6</t>
+  </si>
+  <si>
+    <t>IIT_SEC-1</t>
+  </si>
+  <si>
+    <t>IIT_SEC-2</t>
+  </si>
+  <si>
+    <t>IIT_SEC-3</t>
+  </si>
+  <si>
+    <t>NCERT_STATUS</t>
+  </si>
+  <si>
+    <t>Particulate Nature of Matter</t>
+  </si>
+  <si>
+    <t>PARTICULATE NATURE OF MATTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NATURE OF MATTER, ELEMENTS,  COMPOUNDS AND MIXTURES: </t>
   </si>
   <si>
     <t>SOME BASIC CONCEPTS OF CHEMISTRY</t>
   </si>
   <si>
-    <t>PARTICULATE NATURE OF MATTER</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NATURE OF MATTER, ELEMENTS,  COMPOUNDS AND MIXTURES: </t>
-  </si>
-  <si>
     <t>STRUCTURE OF ATOM</t>
-  </si>
-  <si>
-    <t>Particulate Nature of Matter</t>
-  </si>
-  <si>
-    <t>IIT SYLLABUS</t>
   </si>
 </sst>
 </file>
@@ -113,7 +113,6 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -227,10 +226,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -552,261 +554,320 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="45" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="35" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" customWidth="1"/>
-    <col min="11" max="11" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="41.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="8" width="14.7109375" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1"/>
+    <col min="10" max="10" width="24.28515625" customWidth="1"/>
+    <col min="14" max="14" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K1" s="4" t="s">
+      <c r="K6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-    </row>
-    <row r="3" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="1" t="s">
+    <row r="7" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="1"/>
+      <c r="B7" s="2"/>
       <c r="C7" s="1" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="14">
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="H1:H2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
     <mergeCell ref="C1:C2"/>
-    <mergeCell ref="K1:K2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="E1:K1 H8:I40">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="K1:N1 K3:N7 C1:I1 C3:I7">
       <formula1>"Not Started,In Progress,Completed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="E3:K7">
-      <formula1>"Not Assigned,In Progress,Completed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/server/master-excel-files/Kailash_CHEMISTRY_Grade 8.xlsx
+++ b/server/master-excel-files/Kailash_CHEMISTRY_Grade 8.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Teachers year plan\ISAP_CHEMISTRY\NCERT_IIT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\teacher-year-plan-app\server\master-excel-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -30,9 +30,6 @@
     <t>JUNE</t>
   </si>
   <si>
-    <t>Not Started</t>
-  </si>
-  <si>
     <t>JULY</t>
   </si>
   <si>
@@ -94,6 +91,9 @@
   </si>
   <si>
     <t>STRUCTURE OF ATOM</t>
+  </si>
+  <si>
+    <t>Not Assigned</t>
   </si>
 </sst>
 </file>
@@ -234,12 +234,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -250,6 +244,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -568,290 +568,285 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="6"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="4"/>
     </row>
     <row r="3" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="K5" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="H1:H2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="I1:I2"/>
@@ -861,10 +856,18 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="H1:H2"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="K1:N1 K3:N7 C1:I1 C3:I7">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="K1:N1 C1:I1">
       <formula1>"Not Started,In Progress,Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="C3:I7 K3:N7">
+      <formula1>"Not Assigned,In Progress,Completed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
